--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.0724571762503</v>
+        <v>5.861774291140673</v>
       </c>
       <c r="D2" t="n">
-        <v>35.96618080479934</v>
+        <v>5.844504380779894</v>
       </c>
       <c r="E2" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F2" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.73773863714201</v>
+        <v>9.707382528535577</v>
       </c>
       <c r="D3" t="n">
-        <v>54.50999966789738</v>
+        <v>8.857874946033323</v>
       </c>
       <c r="E3" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F3" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.98519784448359</v>
+        <v>8.772594649728584</v>
       </c>
       <c r="D4" t="n">
-        <v>48.5624401560141</v>
+        <v>7.891396525352291</v>
       </c>
       <c r="E4" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F4" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.16107643286761</v>
+        <v>5.876174920340987</v>
       </c>
       <c r="D5" t="n">
-        <v>36.1932798646728</v>
+        <v>5.88140797800933</v>
       </c>
       <c r="E5" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F5" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.3865024408617</v>
+        <v>4.775306646640027</v>
       </c>
       <c r="D6" t="n">
-        <v>29.70246503530017</v>
+        <v>4.826650568236278</v>
       </c>
       <c r="E6" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F6" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.1440482074139</v>
+        <v>5.873407833704758</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62237880978927</v>
+        <v>6.276136556590756</v>
       </c>
       <c r="E7" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F7" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>51.79349488117615</v>
+        <v>8.416442918191125</v>
       </c>
       <c r="D8" t="n">
-        <v>33.58065838939214</v>
+        <v>5.456856988276223</v>
       </c>
       <c r="E8" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F8" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.074417270027</v>
+        <v>1.637092806379388</v>
       </c>
       <c r="D9" t="n">
-        <v>7.962204645262681</v>
+        <v>1.293858254855186</v>
       </c>
       <c r="E9" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F9" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>69.46112629698281</v>
+        <v>11.28743302325971</v>
       </c>
       <c r="D10" t="n">
-        <v>17.69961919824848</v>
+        <v>2.876188119715378</v>
       </c>
       <c r="E10" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F10" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.91012299261584</v>
+        <v>7.785394986300074</v>
       </c>
       <c r="D11" t="n">
-        <v>6.436596088867702</v>
+        <v>1.045946864441002</v>
       </c>
       <c r="E11" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F11" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.90162013512955</v>
+        <v>5.509013271958553</v>
       </c>
       <c r="D12" t="n">
-        <v>19.25084674264075</v>
+        <v>3.128262595679122</v>
       </c>
       <c r="E12" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F12" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>78.0392007093011</v>
+        <v>12.68137011526143</v>
       </c>
       <c r="D13" t="n">
-        <v>12.74764730898636</v>
+        <v>2.071492687710283</v>
       </c>
       <c r="E13" t="n">
-        <v>17.94645971038242</v>
+        <v>2.916299702937144</v>
       </c>
       <c r="F13" t="n">
-        <v>14.95145258895501</v>
+        <v>2.429611045705189</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
